--- a/output/pdf_financials_xlsx/JEV.xlsx
+++ b/output/pdf_financials_xlsx/JEV.xlsx
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.306603</v>
+        <v>-0.306603</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.379154</v>
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.306603</v>
+        <v>-0.306603</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.379154</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.306603</v>
+        <v>-0.306603</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.379154</v>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-6.13206</v>
+        <v>6.13206</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>12.638467</v>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.306603</v>
+        <v>-0.306603</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.379154</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.306603</v>
+        <v>-0.306603</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.379154</v>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -3723,19 +3723,19 @@
         <v>32.487948</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>12.643186</v>
+        <v>0.007878</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>14.545469</v>
+        <v>1.55868</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>18.640555</v>
+        <v>3.521994</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>16.689363</v>
+        <v>3.500393</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>15.955727</v>
+        <v>3.725612</v>
       </c>
       <c r="P61" s="3" t="n">
         <v>8.263272000000001</v>
@@ -5416,7 +5416,7 @@
         <v>5.822502</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>6.764395</v>
       </c>
     </row>
     <row r="93">
@@ -9348,7 +9348,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -10111,7 +10115,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherNonCurrentAssets</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -10556,7 +10560,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherNonCurrentAssets</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -11636,7 +11640,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherNonCurrentAssets</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -13175,7 +13179,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherNonCurrentAssets</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -16207,7 +16211,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -56972,7 +56980,7 @@
         </is>
       </c>
       <c r="E551" s="5" t="n">
-        <v>0.306603</v>
+        <v>-0.306603</v>
       </c>
       <c r="F551" s="5" t="n">
         <v>-0.379154</v>

--- a/output/pdf_financials_xlsx/JEV.xlsx
+++ b/output/pdf_financials_xlsx/JEV.xlsx
@@ -1024,28 +1024,28 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002909</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.006857</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.013575</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.01019</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.008321</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>2.4e-05</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.00016</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -1886,28 +1886,28 @@
         <v>-0.306603</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.379154</v>
+        <v>-0.382063</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.346567</v>
+        <v>-0.353424</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.692305</v>
+        <v>-1.70588</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.370642</v>
+        <v>0.360452</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.790032</v>
+        <v>0.781711</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-6.732776</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-4.06124</v>
+        <v>-4.061264</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-8.529519000000001</v>
+        <v>-8.529679</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-20.128</v>
@@ -1956,22 +1956,22 @@
         <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.076657</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.11568</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.023737</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.407632</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.533123</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.628938</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>0.964153</v>
@@ -1990,40 +1990,40 @@
         <v>-0.306603</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.379154</v>
+        <v>-0.382063</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.346567</v>
+        <v>-0.353424</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.692305</v>
+        <v>-1.70588</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.370642</v>
+        <v>0.360452</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.790032</v>
+        <v>0.781711</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-6.732776</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-4.06124</v>
+        <v>-3.984607</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-8.529519000000001</v>
+        <v>-8.413999</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-20.128</v>
+        <v>-20.104263</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-4.940722</v>
+        <v>-4.53309</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-4.515305</v>
+        <v>-3.982182</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-7.321633</v>
+        <v>-6.692695</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-6.476071</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.409968</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.843478</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.35452</v>
@@ -2277,34 +2277,34 @@
         <v>1.675131</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>5.04517</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>5.292783</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>3.963688</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.579451</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2.782234</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>4.896074</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.349638</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.036529</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.072073</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.08752600000000001</v>
       </c>
     </row>
     <row r="35">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.409968</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.843478</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.35452</v>
@@ -2381,34 +2381,34 @@
         <v>1.675131</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>5.04517</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>5.292783</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>3.963688</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.579451</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>2.782234</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>4.896074</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.349638</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.036529</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.072073</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.08752600000000001</v>
       </c>
     </row>
     <row r="37">
@@ -2990,10 +2990,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.409968</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.845177</v>
+        <v>0.001699</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.001365</v>
@@ -3005,34 +3005,34 @@
         <v>0.062418</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>5.31058</v>
+        <v>0.26541</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>5.446786</v>
+        <v>0.154003</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>4.05202</v>
+        <v>0.08833199999999999</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.591068</v>
+        <v>0.011617</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.792046</v>
+        <v>0.009812</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>4.93769</v>
+        <v>0.041616</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.393153</v>
+        <v>0.043515</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.150137</v>
+        <v>0.113608</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.162066</v>
+        <v>0.089993</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.09160799999999999</v>
+        <v>0.004082</v>
       </c>
     </row>
     <row r="49">
@@ -3723,19 +3723,19 @@
         <v>32.487948</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.007878</v>
+        <v>12.643186</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>1.55868</v>
+        <v>14.545469</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>3.521994</v>
+        <v>18.640555</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>3.500393</v>
+        <v>16.689363</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>3.725612</v>
+        <v>15.955727</v>
       </c>
       <c r="P61" s="3" t="n">
         <v>8.263272000000001</v>
@@ -5766,22 +5766,22 @@
         <v>0</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.076657</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.11568</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.023737</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.407632</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.533123</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.628938</v>
       </c>
       <c r="O100" s="3" t="n">
         <v>0.964153</v>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>OtherNonCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>OtherNonCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>OtherNonCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -13179,7 +13179,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>OtherNonCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -20033,7 +20033,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
@@ -24688,7 +24688,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -26104,7 +26104,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -27712,7 +27712,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -29696,7 +29696,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -41371,7 +41371,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -43052,7 +43052,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -43400,7 +43400,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -44013,7 +44013,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -45623,7 +45623,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -50847,7 +50847,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -56883,7 +56883,7 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">

--- a/output/pdf_financials_xlsx/JEV.xlsx
+++ b/output/pdf_financials_xlsx/JEV.xlsx
@@ -1299,7 +1299,7 @@
         <v>-0.752</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.718</v>
+        <v>-0.718</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>0.003229</v>
@@ -2580,10 +2580,10 @@
         <v>0</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.002529</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.00797</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>0</v>
@@ -2635,7 +2635,7 @@
         <v>0.037862</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.108213</v>
+        <v>0.116183</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>0.404797</v>
@@ -2999,7 +2999,7 @@
         <v>0.001365</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.043967</v>
+        <v>0.035997</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.062418</v>
@@ -4008,25 +4008,25 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.023344</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.0135</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.042657</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.063655</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.11413</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>0</v>
@@ -6353,7 +6353,7 @@
         <v>0</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001745</v>
       </c>
       <c r="O111" s="3" t="n">
         <v>0</v>
@@ -7579,7 +7579,7 @@
         <v>0</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001745</v>
       </c>
       <c r="O134" s="3" t="n">
         <v>0</v>
@@ -7631,7 +7631,7 @@
         <v>-3.263782</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-3.197453</v>
+        <v>-3.199198</v>
       </c>
       <c r="O135" s="3" t="n">
         <v>-3.032229</v>
@@ -25137,7 +25137,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -46956,7 +46960,11 @@
           <t>Deferred income tax recovery (expense) 16</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E441" t="inlineStr">
         <is>
           <t>-</t>
@@ -48402,7 +48410,11 @@
           <t>Deferred income tax recovery 19</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
           <t>-</t>
